--- a/docs/StructureDefinition-BRPlanoCuidados-1.0.xlsx
+++ b/docs/StructureDefinition-BRPlanoCuidados-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -368,7 +368,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -503,7 +503,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -961,7 +961,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1039,7 +1039,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1124,7 +1124,7 @@
     <t>CarePlan.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1164,7 +1164,7 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1249,7 +1249,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1283,7 +1283,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition)
+    <t xml:space="preserve">Reference(Condition|4.0.1)
 </t>
   </si>
   <si>
@@ -1336,7 +1336,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1358,7 +1358,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
   </si>
   <si>
@@ -1445,7 +1445,7 @@
     <t>Identifies the results of the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1497,7 +1497,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|MedicationRequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
+    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
 </t>
   </si>
   <si>
@@ -1569,7 +1569,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1603,7 +1603,7 @@
     <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1630,7 +1630,7 @@
     <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1639,7 +1639,7 @@
     <t>CarePlan.activity.detail.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1760,7 +1760,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1785,7 +1785,7 @@
     <t>CarePlan.activity.detail.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|RelatedPerson|Patient|CareTeam|HealthcareService|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|RelatedPerson|4.0.1|Patient|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1811,7 +1811,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>What is to be administered/supplied</t>
@@ -1823,7 +1823,7 @@
     <t>A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1839,7 +1839,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2382,7 +2382,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>184</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>218</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>223</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>244</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>254</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>272</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>279</v>
       </c>
@@ -13102,12 +13102,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN95">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
